--- a/Result/profitability/1717.xlsx
+++ b/Result/profitability/1717.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.34</v>
       </c>
       <c r="M2" t="n">
-        <v>0.365</v>
+        <v>0.40625</v>
       </c>
       <c r="N2" t="n">
-        <v>20.26375</v>
+        <v>20.8875</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>0.37875</v>
+        <v>0.4175</v>
       </c>
       <c r="N3" t="n">
-        <v>19.99</v>
+        <v>20.6325</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42125</v>
+        <v>0.47375</v>
       </c>
       <c r="N4" t="n">
-        <v>19.7025</v>
+        <v>20.2525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4025</v>
+        <v>0.455</v>
       </c>
       <c r="N5" t="n">
-        <v>18.79125</v>
+        <v>19.2875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>1.24</v>
       </c>
       <c r="M6" t="n">
-        <v>0.52</v>
+        <v>0.54875</v>
       </c>
       <c r="N6" t="n">
-        <v>18.29875</v>
+        <v>18.935</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.89</v>
       </c>
       <c r="M7" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="N7" t="n">
-        <v>18.465</v>
+        <v>18.905</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.88</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6399999999999999</v>
+        <v>0.68375</v>
       </c>
       <c r="N8" t="n">
-        <v>18.725</v>
+        <v>19.05625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.52</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6587500000000001</v>
+        <v>0.6587499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>18.65375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1717</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11926</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8967</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2958</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1024</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.59%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>145</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1169</v>
+      </c>
+      <c r="K75" t="n">
+        <v>847</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9459459459459458</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.649999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1195848375451263</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.969999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1904990403071016</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
